--- a/portal/templates/lumian-leads-import-vorlage.xlsx
+++ b/portal/templates/lumian-leads-import-vorlage.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import" sheetId="1" r:id="R6de424cb2b5f4b89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hinweise" sheetId="2" r:id="Ra714a8c670ce4879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import" sheetId="1" r:id="R2a78c2b9fde34f2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hinweise" sheetId="2" r:id="Rff70d2d863854117"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -41,7 +41,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -58,6 +58,16 @@
         <x:fgColor rgb="FF0B5E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B5E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD5EDF5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -66,7 +76,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -129,6 +139,28 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -315,24 +347,28 @@
     <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="5" t="str">
         <x:v>Lumian Leads Import Vorlage</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str"/>
-      <x:c r="C1" s="5" t="str"/>
-      <x:c r="D1" s="5" t="str"/>
-      <x:c r="E1" s="5" t="str"/>
-      <x:c r="F1" s="5" t="str"/>
-      <x:c r="G1" s="5" t="str"/>
-      <x:c r="H1" s="5" t="str"/>
-      <x:c r="I1" s="5" t="str"/>
-      <x:c r="J1" s="5" t="str"/>
-      <x:c r="K1" s="5" t="str"/>
-    </x:row>
-    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5"/>
+      <x:c r="H1" s="5"/>
+      <x:c r="I1" s="5"/>
+      <x:c r="J1" s="5"/>
+      <x:c r="K1" s="5"/>
+      <x:c r="L1"/>
+      <x:c r="M1"/>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="14" t="str">
         <x:v>Name</x:v>
       </x:c>
@@ -366,15 +402,21 @@
       <x:c r="K2" s="14" t="str">
         <x:v>Notizen</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3">
+      <x:c r="L2" s="36" t="str">
+        <x:v>LeadGewonnenDurch</x:v>
+      </x:c>
+      <x:c r="M2" s="36" t="str">
+        <x:v>Zustaendig</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="21" t="str">
         <x:v>Peter Beispiel</x:v>
       </x:c>
       <x:c r="B3" s="21" t="str">
         <x:v>079 123 45 67</x:v>
       </x:c>
-      <x:c r="C3" s="21" t="str"/>
+      <x:c r="C3" s="21"/>
       <x:c r="D3" s="21" t="str">
         <x:v>Beispielweg 2</x:v>
       </x:c>
@@ -385,7 +427,7 @@
         <x:v>Fensterreinigung</x:v>
       </x:c>
       <x:c r="G3" s="21" t="str">
-        <x:v>Google</x:v>
+        <x:v>Tür-zu-Tür</x:v>
       </x:c>
       <x:c r="H3" s="21" t="str">
         <x:v>350</x:v>
@@ -398,6 +440,12 @@
       </x:c>
       <x:c r="K3" s="21" t="str">
         <x:v>Besichtigung nötig</x:v>
+      </x:c>
+      <x:c r="L3" s="39" t="str">
+        <x:v>noah</x:v>
+      </x:c>
+      <x:c r="M3" s="39" t="str">
+        <x:v>timo</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2289,7 +2337,7 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:K1"/>
+    <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="F3:F502">
@@ -2301,7 +2349,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6815b9f5db384cc0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13ca9639ced1491e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2313,28 +2361,38 @@
     <x:col min="1" max="1" width="90" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="28" t="str">
+    <x:row r="1" ht="18" hidden="0" customHeight="1">
+      <x:c r="A1" s="31" t="str">
         <x:v>Hinweise</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="20" t="str">
         <x:v>Pflicht: Name oder Telefon. Alles andere kann später im Portal ergänzt werden.</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="20" t="str">
         <x:v>Datum/Termin bitte in Schweizer Format eingeben: TT.MM.JJJJ oder TT.MM.JJJJ HH:MM.</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="20" t="str">
         <x:v>EmpfohlenVon kann leer bleiben oder eine Lumian-Nr. enthalten, z.B. LM1001.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="20" t="str">
+        <x:v>LeadGewonnenDurch und Zustaendig können Benutzername/Kürzel oder den exakten Mitarbeiternamen enthalten, z.B. noah, timo oder Jana Müller.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="20" t="str">
+        <x:v>Die Standard-Akquiseprovision wird automatisch aus dem Profil von LeadGewonnenDurch übernommen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="20" t="str">
         <x:v>Betrag ohne CHF schreiben, z.B. 350.</x:v>
       </x:c>
     </x:row>
